--- a/data/HeureAdmin.xlsx
+++ b/data/HeureAdmin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fwb365.sharepoint.com/sites/CPM-PrestationsAgentsCPM/Shared Documents/Prestations Agents CPM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{8C43EBD8-942C-4732-A3D9-C9D8A542A150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21C0B190-C45F-4648-AA5D-E835E7955CB0}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{8C43EBD8-942C-4732-A3D9-C9D8A542A150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DEE89EE-8764-4997-A0E8-2C94DCFC26A5}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="2" r:id="rId1"/>
@@ -327,32 +327,37 @@
         </row>
         <row r="6">
           <cell r="K6">
-            <v>1.0359944698703281</v>
+            <v>1.0484944698703282</v>
           </cell>
         </row>
         <row r="7">
           <cell r="K7">
-            <v>1.0228000254258836</v>
+            <v>1.0353000254258837</v>
           </cell>
         </row>
         <row r="8">
           <cell r="K8">
-            <v>1.0054389143147724</v>
+            <v>1.0179389143147726</v>
           </cell>
         </row>
         <row r="9">
           <cell r="K9">
-            <v>0.95739969862849783</v>
+            <v>0.96994054830170073</v>
           </cell>
         </row>
         <row r="10">
           <cell r="K10">
-            <v>0.99489969862849781</v>
+            <v>0.99355165941281187</v>
           </cell>
         </row>
         <row r="11">
           <cell r="K11">
-            <v>0.66920525418405341</v>
+            <v>0.66785721496836747</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.56408737369852624</v>
           </cell>
         </row>
         <row r="19">
@@ -462,6 +467,11 @@
             <v>0.58198412698412694</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.73545634920634917</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -569,6 +579,11 @@
             <v>1.6560555555555554</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>1.5324444444444443</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -676,6 +691,11 @@
             <v>0.98789800175669729</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>1.1476202239789195</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -783,6 +803,11 @@
             <v>0.81874999999999976</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.96041666666666647</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -890,6 +915,11 @@
             <v>-0.65509469696969702</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>-0.40509469696969702</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19">
             <v>0</v>
@@ -947,6 +977,11 @@
             <v>0.43402118134647261</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.54791007023536153</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1054,6 +1089,11 @@
             <v>0.66527777777777797</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.79027777777777797</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1131,11 +1171,16 @@
             <v>0.40833333333333333</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.6166666666666667</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="9">
         <row r="2">
-          <cell r="F2">
-            <v>0.85972222222222217</v>
+          <cell r="F2" t="str">
+            <v xml:space="preserve"> </v>
           </cell>
         </row>
         <row r="5">
@@ -1171,6 +1216,11 @@
         <row r="11">
           <cell r="K11">
             <v>2.5080176767676767</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>1.7135732323232322</v>
           </cell>
         </row>
         <row r="19">
@@ -1280,6 +1330,11 @@
             <v>1.4895833333333333</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>1.6187499999999999</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1387,6 +1442,11 @@
             <v>0.97844254080524107</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>1.2284425408052411</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1469,6 +1529,11 @@
             <v>0.38592171717171719</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.4030844155844156</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="13">
         <row r="2">
@@ -1511,6 +1576,11 @@
             <v>1.2714909688582463</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>1.1103798577471351</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1615,7 +1685,12 @@
         </row>
         <row r="11">
           <cell r="K11">
-            <v>0.5632575757575764</v>
+            <v>0.69520202020202082</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.74936868686868752</v>
           </cell>
         </row>
         <row r="19">
@@ -1725,6 +1800,11 @@
             <v>0.38244949494949465</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.26300505050505019</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1832,6 +1912,11 @@
             <v>9.2208333333333332</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>9.4708333333333332</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1939,6 +2024,11 @@
             <v>0.41425296195033035</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.5073085175058859</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -2007,8 +2097,8 @@
       </sheetData>
       <sheetData sheetId="18">
         <row r="2">
-          <cell r="F2">
-            <v>0.24791666666666684</v>
+          <cell r="F2" t="str">
+            <v xml:space="preserve"> </v>
           </cell>
         </row>
         <row r="5">
@@ -2044,6 +2134,11 @@
         <row r="11">
           <cell r="K11">
             <v>2.0709722222222213</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>1.6855555555555548</v>
           </cell>
         </row>
         <row r="19">
@@ -2151,6 +2246,11 @@
         <row r="11">
           <cell r="K11">
             <v>1.3366666666666667</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>1.4908333333333332</v>
           </cell>
         </row>
         <row r="19">
@@ -2229,21 +2329,21 @@
   <autoFilter ref="A1:N21" xr:uid="{C7300799-99B8-4EB6-AE56-6C90EDB091F8}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{EB6C97B9-1CA8-48D2-9510-545DC67E1BBF}" name="Agent"/>
-    <tableColumn id="2" xr3:uid="{C66CE8F8-4087-4061-8EA3-AB9D0A8E447C}" name="Solde 31/08" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{9ECC8A47-2A4B-4D34-B13F-78D39587CA33}" name="Janvier" dataDxfId="11">
+    <tableColumn id="2" xr3:uid="{C66CE8F8-4087-4061-8EA3-AB9D0A8E447C}" name="Solde 31/08" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{9ECC8A47-2A4B-4D34-B13F-78D39587CA33}" name="Janvier" dataDxfId="12">
       <calculatedColumnFormula>[1]BLAVIER!$K$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B672229B-47A9-4DDA-97B0-42F7FFE6755D}" name="Février" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{0D9FFA72-0E5C-462A-BC84-09657AFC2047}" name="Mars" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{6DD2E5EB-3749-4C8D-8925-14083FF7A139}" name="Avril" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{A20FEEC3-C73B-459B-97A2-74915F126C89}" name="Mai" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{8A000117-6DB3-4A3E-9E33-123A99327AE5}" name="Juin" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{0685936A-96FA-4393-87B0-7A35C9243EA4}" name="Juillet" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{70FA5B23-5F41-4134-AFA6-6CF2DBDA3A0B}" name="Août" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{5B0EE54E-7CF9-4BE7-98F7-31268BFF16C0}" name="Septembre" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{990F648E-0595-4475-9CA0-5C902A84D4D1}" name="Octobre" dataDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{D412263F-C5F1-4334-8DE9-BAF8FA623F7F}" name="Novembre" dataDxfId="1"/>
-    <tableColumn id="14" xr3:uid="{A063487C-7F33-4DF7-8940-9A8E590D6F35}" name="Décembre" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{B672229B-47A9-4DDA-97B0-42F7FFE6755D}" name="Février" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{0D9FFA72-0E5C-462A-BC84-09657AFC2047}" name="Mars" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{6DD2E5EB-3749-4C8D-8925-14083FF7A139}" name="Avril" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{A20FEEC3-C73B-459B-97A2-74915F126C89}" name="Mai" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{8A000117-6DB3-4A3E-9E33-123A99327AE5}" name="Juin" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{0685936A-96FA-4393-87B0-7A35C9243EA4}" name="Juillet" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{70FA5B23-5F41-4134-AFA6-6CF2DBDA3A0B}" name="Août" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{5B0EE54E-7CF9-4BE7-98F7-31268BFF16C0}" name="Septembre" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{990F648E-0595-4475-9CA0-5C902A84D4D1}" name="Octobre" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{D412263F-C5F1-4334-8DE9-BAF8FA623F7F}" name="Novembre" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{A063487C-7F33-4DF7-8940-9A8E590D6F35}" name="Décembre" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2264,11 +2364,11 @@
     <tableColumn id="4" xr3:uid="{73890115-5FC3-4C52-9738-5535D8C89AA6}" name="Mai" dataDxfId="20"/>
     <tableColumn id="3" xr3:uid="{C3AD0FE6-38FB-4AF2-A2FC-CD8C6AF1D34A}" name="Juin" dataDxfId="19"/>
     <tableColumn id="9" xr3:uid="{2CF88554-1C99-48F6-A58C-B366489DC66A}" name="Juillet" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{92839190-8610-4DAD-9F46-735A99F92CBC}" name="Août" dataDxfId="17"/>
-    <tableColumn id="11" xr3:uid="{29BF599E-3D07-4D08-9AF4-0E200B9474AF}" name="Septembre" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{69B209A5-8270-436F-A131-3A88CE5DD18E}" name="Octobre" dataDxfId="15"/>
-    <tableColumn id="13" xr3:uid="{5495805F-AD9C-4F16-87DB-C13BD64B4392}" name="Novembre" dataDxfId="14"/>
-    <tableColumn id="14" xr3:uid="{4BC933CC-966E-4C7C-A940-6828309FC481}" name="Décembre" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{92839190-8610-4DAD-9F46-735A99F92CBC}" name="Août" dataDxfId="0"/>
+    <tableColumn id="11" xr3:uid="{29BF599E-3D07-4D08-9AF4-0E200B9474AF}" name="Septembre" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{69B209A5-8270-436F-A131-3A88CE5DD18E}" name="Octobre" dataDxfId="16"/>
+    <tableColumn id="13" xr3:uid="{5495805F-AD9C-4F16-87DB-C13BD64B4392}" name="Novembre" dataDxfId="15"/>
+    <tableColumn id="14" xr3:uid="{4BC933CC-966E-4C7C-A940-6828309FC481}" name="Décembre" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3798,29 +3898,32 @@
       </c>
       <c r="D2" s="1">
         <f>[1]BECKERS!$K$6</f>
-        <v>1.0359944698703281</v>
+        <v>1.0484944698703282</v>
       </c>
       <c r="E2" s="1">
         <f>[1]BECKERS!$K$7</f>
-        <v>1.0228000254258836</v>
+        <v>1.0353000254258837</v>
       </c>
       <c r="F2" s="1">
         <f>[1]BECKERS!$K$8</f>
-        <v>1.0054389143147724</v>
+        <v>1.0179389143147726</v>
       </c>
       <c r="G2" s="1">
         <f>[1]BECKERS!$K$9</f>
-        <v>0.95739969862849783</v>
+        <v>0.96994054830170073</v>
       </c>
       <c r="H2" s="1">
         <f>[1]BECKERS!$K$10</f>
-        <v>0.99489969862849781</v>
+        <v>0.99355165941281187</v>
       </c>
       <c r="I2" s="1">
         <f>[1]BECKERS!$K$11</f>
-        <v>0.66920525418405341</v>
-      </c>
-      <c r="J2" s="1"/>
+        <v>0.66785721496836747</v>
+      </c>
+      <c r="J2" s="1">
+        <f>[1]BECKERS!$K$12</f>
+        <v>0.56408737369852624</v>
+      </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -3862,7 +3965,10 @@
         <f>[1]BLAVIER!$K$11</f>
         <v>0.58198412698412694</v>
       </c>
-      <c r="J3" s="1"/>
+      <c r="J3" s="1">
+        <f>[1]BLAVIER!$K$12</f>
+        <v>0.73545634920634917</v>
+      </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -3904,7 +4010,10 @@
         <f>[1]BREUCKER!$K$11</f>
         <v>1.6560555555555554</v>
       </c>
-      <c r="J4" s="1"/>
+      <c r="J4" s="1">
+        <f>[1]BREUCKER!$K$12</f>
+        <v>1.5324444444444443</v>
+      </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -3946,7 +4055,10 @@
         <f>[1]BRUNIN!$K$11</f>
         <v>0.98789800175669729</v>
       </c>
-      <c r="J5" s="1"/>
+      <c r="J5" s="1">
+        <f>[1]BRUNIN!$K$12</f>
+        <v>1.1476202239789195</v>
+      </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -3988,7 +4100,10 @@
         <f>[1]DEWEZ!$K$11</f>
         <v>0.81874999999999976</v>
       </c>
-      <c r="J6" s="1"/>
+      <c r="J6" s="1">
+        <f>[1]DEWEZ!$K$12</f>
+        <v>0.96041666666666647</v>
+      </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -4030,7 +4145,10 @@
         <f>[1]HENDRICKX!$K$11</f>
         <v>-0.65509469696969702</v>
       </c>
-      <c r="J7" s="1"/>
+      <c r="J7" s="1">
+        <f>[1]HENDRICKX!$K$12</f>
+        <v>-0.40509469696969702</v>
+      </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -4072,7 +4190,10 @@
         <f>[1]HOEBEKE!$K$11</f>
         <v>0.43402118134647261</v>
       </c>
-      <c r="J8" s="1"/>
+      <c r="J8" s="1">
+        <f>[1]HOEBEKE!$K$12</f>
+        <v>0.54791007023536153</v>
+      </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -4114,7 +4235,10 @@
         <f>[1]JOIRIS!$K$11</f>
         <v>0.66527777777777797</v>
       </c>
-      <c r="J9" s="1"/>
+      <c r="J9" s="1">
+        <f>[1]JOIRIS!$K$12</f>
+        <v>0.79027777777777797</v>
+      </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -4138,7 +4262,10 @@
         <f>[1]KAISER!$K$11</f>
         <v>0.40833333333333333</v>
       </c>
-      <c r="J10" s="1"/>
+      <c r="J10" s="1">
+        <f>[1]KAISER!$K$12</f>
+        <v>0.6166666666666667</v>
+      </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -4148,9 +4275,9 @@
       <c r="A11" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="1" t="str">
         <f>[1]LAMBERT!$F$2</f>
-        <v>0.85972222222222217</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="C11" s="1">
         <f>[1]LAMBERT!$K$5</f>
@@ -4180,7 +4307,10 @@
         <f>[1]LAMBERT!$K$11</f>
         <v>2.5080176767676767</v>
       </c>
-      <c r="J11" s="1"/>
+      <c r="J11" s="1">
+        <f>[1]LAMBERT!$K$12</f>
+        <v>1.7135732323232322</v>
+      </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -4222,7 +4352,10 @@
         <f>[1]LEBOUTTE!$K$11</f>
         <v>1.4895833333333333</v>
       </c>
-      <c r="J12" s="1"/>
+      <c r="J12" s="1">
+        <f>[1]LEBOUTTE!$K$12</f>
+        <v>1.6187499999999999</v>
+      </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -4264,7 +4397,10 @@
         <f>[1]MAGNUS!$K$11</f>
         <v>0.97844254080524107</v>
       </c>
-      <c r="J13" s="1"/>
+      <c r="J13" s="1">
+        <f>[1]MAGNUS!$K$12</f>
+        <v>1.2284425408052411</v>
+      </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -4291,7 +4427,10 @@
         <f>[1]NDEMA!$K$11</f>
         <v>0.38592171717171719</v>
       </c>
-      <c r="J14" s="1"/>
+      <c r="J14" s="1">
+        <f>[1]NDEMA!$K$12</f>
+        <v>0.4030844155844156</v>
+      </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -4333,7 +4472,10 @@
         <f>[1]NOLET!$K$11</f>
         <v>1.2714909688582463</v>
       </c>
-      <c r="J15" s="1"/>
+      <c r="J15" s="1">
+        <f>[1]NOLET!$K$12</f>
+        <v>1.1103798577471351</v>
+      </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -4373,9 +4515,12 @@
       </c>
       <c r="I16" s="1">
         <f>[1]PAQUAY!$K$11</f>
-        <v>0.5632575757575764</v>
-      </c>
-      <c r="J16" s="1"/>
+        <v>0.69520202020202082</v>
+      </c>
+      <c r="J16" s="1">
+        <f>[1]PAQUAY!$K$12</f>
+        <v>0.74936868686868752</v>
+      </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -4417,7 +4562,10 @@
         <f>[1]POIRET!$K$11</f>
         <v>0.38244949494949465</v>
       </c>
-      <c r="J17" s="1"/>
+      <c r="J17" s="1">
+        <f>[1]POIRET!$K$12</f>
+        <v>0.26300505050505019</v>
+      </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -4459,7 +4607,10 @@
         <f>[1]PRETTO!$K$11</f>
         <v>9.2208333333333332</v>
       </c>
-      <c r="J18" s="1"/>
+      <c r="J18" s="1">
+        <f>[1]PRETTO!$K$12</f>
+        <v>9.4708333333333332</v>
+      </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -4501,7 +4652,10 @@
         <f>[1]RENARD!$K$11</f>
         <v>0.41425296195033035</v>
       </c>
-      <c r="J19" s="1"/>
+      <c r="J19" s="1">
+        <f>[1]RENARD!$K$12</f>
+        <v>0.5073085175058859</v>
+      </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -4511,9 +4665,9 @@
       <c r="A20" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="1" t="str">
         <f>[1]STOURME!$F$2</f>
-        <v>0.24791666666666684</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="C20" s="1">
         <f>[1]STOURME!$K$5</f>
@@ -4543,7 +4697,10 @@
         <f>[1]STOURME!$K$11</f>
         <v>2.0709722222222213</v>
       </c>
-      <c r="J20" s="1"/>
+      <c r="J20" s="1">
+        <f>[1]STOURME!$K$12</f>
+        <v>1.6855555555555548</v>
+      </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -4585,7 +4742,10 @@
         <f>[1]VALDES!$K$11</f>
         <v>1.3366666666666667</v>
       </c>
-      <c r="J21" s="1"/>
+      <c r="J21" s="1">
+        <f>[1]VALDES!$K$12</f>
+        <v>1.4908333333333332</v>
+      </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -4604,15 +4764,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100937BC018F9DBE74C924557264AE521C8" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df6304fc725e62364016da26349e6aa2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1af87cbf-0b42-4b26-9f6b-99e2f2c26033" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="24110c7d026aeb2113c3cc5af0e0c47a" ns2:_="">
     <xsd:import namespace="1af87cbf-0b42-4b26-9f6b-99e2f2c26033"/>
@@ -4796,6 +4947,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -4807,14 +4967,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5359EC-D85E-4EE8-994B-A84A38643895}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69449F73-ECCA-4049-9F77-5F6BD292D3D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4832,6 +4984,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5359EC-D85E-4EE8-994B-A84A38643895}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43162B4C-8036-4FD3-B02E-9FAB6E06A7E9}">
   <ds:schemaRefs>

--- a/data/HeureAdmin.xlsx
+++ b/data/HeureAdmin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fwb365.sharepoint.com/sites/CPM-PrestationsAgentsCPM/Shared Documents/Prestations Agents CPM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{8C43EBD8-942C-4732-A3D9-C9D8A542A150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DEE89EE-8764-4997-A0E8-2C94DCFC26A5}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{8C43EBD8-942C-4732-A3D9-C9D8A542A150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{690EC2E3-10E4-4B9E-B9F4-084C38C4D01B}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="2" r:id="rId1"/>
@@ -360,6 +360,11 @@
             <v>0.56408737369852624</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.44533737369852622</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -459,17 +464,22 @@
         </row>
         <row r="10">
           <cell r="K10">
-            <v>0.85212301587301587</v>
+            <v>1.0090674603174603</v>
           </cell>
         </row>
         <row r="11">
           <cell r="K11">
-            <v>0.58198412698412694</v>
+            <v>0.73892857142857138</v>
           </cell>
         </row>
         <row r="12">
           <cell r="K12">
-            <v>0.73545634920634917</v>
+            <v>0.89240079365079361</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.95906746031746026</v>
           </cell>
         </row>
         <row r="19">
@@ -584,6 +594,11 @@
             <v>1.5324444444444443</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>1.417861111111111</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -696,6 +711,11 @@
             <v>1.1476202239789195</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>1.1583525472112428</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -808,6 +828,11 @@
             <v>0.96041666666666647</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>1.1124999999999998</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -920,6 +945,11 @@
             <v>-0.40509469696969702</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>-0.20509469696969701</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19">
             <v>0</v>
@@ -982,6 +1012,11 @@
             <v>0.54791007023536153</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.75552370659899792</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1094,6 +1129,11 @@
             <v>0.79027777777777797</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.75555555555555576</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1176,6 +1216,11 @@
             <v>0.6166666666666667</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.78333333333333333</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="9">
         <row r="2">
@@ -1223,6 +1268,11 @@
             <v>1.7135732323232322</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>1.9186237373737374</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1335,6 +1385,11 @@
             <v>1.6187499999999999</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>1.4715277777777778</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1447,6 +1502,11 @@
             <v>1.2284425408052411</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>1.1504122377749382</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1534,6 +1594,11 @@
             <v>0.4030844155844156</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.16994047619047623</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="13">
         <row r="2">
@@ -1581,6 +1646,11 @@
             <v>1.1103798577471351</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>1.338157635524913</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1693,6 +1763,11 @@
             <v>0.74936868686868752</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.85145202020202082</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1805,6 +1880,11 @@
             <v>0.26300505050505019</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.40119949494949464</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1873,8 +1953,8 @@
       </sheetData>
       <sheetData sheetId="16">
         <row r="2">
-          <cell r="F2">
-            <v>2.1041666666666661</v>
+          <cell r="F2" t="str">
+            <v xml:space="preserve"> </v>
           </cell>
         </row>
         <row r="5">
@@ -1914,7 +1994,12 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>9.4708333333333332</v>
+            <v>7.6624999999999996</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>7.1708333333333334</v>
           </cell>
         </row>
         <row r="19">
@@ -2029,6 +2114,11 @@
             <v>0.5073085175058859</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.65105851750588584</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -2141,6 +2231,11 @@
             <v>1.6855555555555548</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>1.6737499999999992</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19">
             <v>1.1111111111111127E-2</v>
@@ -2251,6 +2346,11 @@
         <row r="12">
           <cell r="K12">
             <v>1.4908333333333332</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.77069444444444435</v>
           </cell>
         </row>
         <row r="19">
@@ -2364,8 +2464,8 @@
     <tableColumn id="4" xr3:uid="{73890115-5FC3-4C52-9738-5535D8C89AA6}" name="Mai" dataDxfId="20"/>
     <tableColumn id="3" xr3:uid="{C3AD0FE6-38FB-4AF2-A2FC-CD8C6AF1D34A}" name="Juin" dataDxfId="19"/>
     <tableColumn id="9" xr3:uid="{2CF88554-1C99-48F6-A58C-B366489DC66A}" name="Juillet" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{92839190-8610-4DAD-9F46-735A99F92CBC}" name="Août" dataDxfId="0"/>
-    <tableColumn id="11" xr3:uid="{29BF599E-3D07-4D08-9AF4-0E200B9474AF}" name="Septembre" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{92839190-8610-4DAD-9F46-735A99F92CBC}" name="Août" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{29BF599E-3D07-4D08-9AF4-0E200B9474AF}" name="Septembre" dataDxfId="0"/>
     <tableColumn id="12" xr3:uid="{69B209A5-8270-436F-A131-3A88CE5DD18E}" name="Octobre" dataDxfId="16"/>
     <tableColumn id="13" xr3:uid="{5495805F-AD9C-4F16-87DB-C13BD64B4392}" name="Novembre" dataDxfId="15"/>
     <tableColumn id="14" xr3:uid="{4BC933CC-966E-4C7C-A940-6828309FC481}" name="Décembre" dataDxfId="14"/>
@@ -3924,7 +4024,10 @@
         <f>[1]BECKERS!$K$12</f>
         <v>0.56408737369852624</v>
       </c>
-      <c r="K2" s="1"/>
+      <c r="K2" s="1">
+        <f>[1]BECKERS!$K$13</f>
+        <v>0.44533737369852622</v>
+      </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -3959,17 +4062,20 @@
       </c>
       <c r="H3" s="1">
         <f>[1]BLAVIER!$K$10</f>
-        <v>0.85212301587301587</v>
+        <v>1.0090674603174603</v>
       </c>
       <c r="I3" s="1">
         <f>[1]BLAVIER!$K$11</f>
-        <v>0.58198412698412694</v>
+        <v>0.73892857142857138</v>
       </c>
       <c r="J3" s="1">
         <f>[1]BLAVIER!$K$12</f>
-        <v>0.73545634920634917</v>
-      </c>
-      <c r="K3" s="1"/>
+        <v>0.89240079365079361</v>
+      </c>
+      <c r="K3" s="1">
+        <f>[1]BLAVIER!$K$13</f>
+        <v>0.95906746031746026</v>
+      </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -4014,7 +4120,10 @@
         <f>[1]BREUCKER!$K$12</f>
         <v>1.5324444444444443</v>
       </c>
-      <c r="K4" s="1"/>
+      <c r="K4" s="1">
+        <f>[1]BREUCKER!$K$13</f>
+        <v>1.417861111111111</v>
+      </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
@@ -4059,7 +4168,10 @@
         <f>[1]BRUNIN!$K$12</f>
         <v>1.1476202239789195</v>
       </c>
-      <c r="K5" s="1"/>
+      <c r="K5" s="1">
+        <f>[1]BRUNIN!$K$13</f>
+        <v>1.1583525472112428</v>
+      </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
@@ -4104,7 +4216,10 @@
         <f>[1]DEWEZ!$K$12</f>
         <v>0.96041666666666647</v>
       </c>
-      <c r="K6" s="1"/>
+      <c r="K6" s="1">
+        <f>[1]DEWEZ!$K$13</f>
+        <v>1.1124999999999998</v>
+      </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
@@ -4149,7 +4264,10 @@
         <f>[1]HENDRICKX!$K$12</f>
         <v>-0.40509469696969702</v>
       </c>
-      <c r="K7" s="1"/>
+      <c r="K7" s="1">
+        <f>[1]HENDRICKX!$K$13</f>
+        <v>-0.20509469696969701</v>
+      </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
@@ -4194,7 +4312,10 @@
         <f>[1]HOEBEKE!$K$12</f>
         <v>0.54791007023536153</v>
       </c>
-      <c r="K8" s="1"/>
+      <c r="K8" s="1">
+        <f>[1]HOEBEKE!$K$13</f>
+        <v>0.75552370659899792</v>
+      </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
@@ -4239,7 +4360,10 @@
         <f>[1]JOIRIS!$K$12</f>
         <v>0.79027777777777797</v>
       </c>
-      <c r="K9" s="1"/>
+      <c r="K9" s="1">
+        <f>[1]JOIRIS!$K$13</f>
+        <v>0.75555555555555576</v>
+      </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
@@ -4266,7 +4390,10 @@
         <f>[1]KAISER!$K$12</f>
         <v>0.6166666666666667</v>
       </c>
-      <c r="K10" s="1"/>
+      <c r="K10" s="1">
+        <f>[1]KAISER!$K$13</f>
+        <v>0.78333333333333333</v>
+      </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -4311,7 +4438,10 @@
         <f>[1]LAMBERT!$K$12</f>
         <v>1.7135732323232322</v>
       </c>
-      <c r="K11" s="1"/>
+      <c r="K11" s="1">
+        <f>[1]LAMBERT!$K$13</f>
+        <v>1.9186237373737374</v>
+      </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -4356,7 +4486,10 @@
         <f>[1]LEBOUTTE!$K$12</f>
         <v>1.6187499999999999</v>
       </c>
-      <c r="K12" s="1"/>
+      <c r="K12" s="1">
+        <f>[1]LEBOUTTE!$K$13</f>
+        <v>1.4715277777777778</v>
+      </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -4401,7 +4534,10 @@
         <f>[1]MAGNUS!$K$12</f>
         <v>1.2284425408052411</v>
       </c>
-      <c r="K13" s="1"/>
+      <c r="K13" s="1">
+        <f>[1]MAGNUS!$K$13</f>
+        <v>1.1504122377749382</v>
+      </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -4431,7 +4567,10 @@
         <f>[1]NDEMA!$K$12</f>
         <v>0.4030844155844156</v>
       </c>
-      <c r="K14" s="1"/>
+      <c r="K14" s="1">
+        <f>[1]NDEMA!$K$13</f>
+        <v>0.16994047619047623</v>
+      </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
@@ -4476,7 +4615,10 @@
         <f>[1]NOLET!$K$12</f>
         <v>1.1103798577471351</v>
       </c>
-      <c r="K15" s="1"/>
+      <c r="K15" s="1">
+        <f>[1]NOLET!$K$13</f>
+        <v>1.338157635524913</v>
+      </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -4521,7 +4663,10 @@
         <f>[1]PAQUAY!$K$12</f>
         <v>0.74936868686868752</v>
       </c>
-      <c r="K16" s="1"/>
+      <c r="K16" s="1">
+        <f>[1]PAQUAY!$K$13</f>
+        <v>0.85145202020202082</v>
+      </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -4566,7 +4711,10 @@
         <f>[1]POIRET!$K$12</f>
         <v>0.26300505050505019</v>
       </c>
-      <c r="K17" s="1"/>
+      <c r="K17" s="1">
+        <f>[1]POIRET!$K$13</f>
+        <v>0.40119949494949464</v>
+      </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
@@ -4575,9 +4723,9 @@
       <c r="A18" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="1" t="str">
         <f>[1]PRETTO!$F$2</f>
-        <v>2.1041666666666661</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="C18" s="1">
         <f>[1]PRETTO!$K$5</f>
@@ -4609,9 +4757,12 @@
       </c>
       <c r="J18" s="1">
         <f>[1]PRETTO!$K$12</f>
-        <v>9.4708333333333332</v>
-      </c>
-      <c r="K18" s="1"/>
+        <v>7.6624999999999996</v>
+      </c>
+      <c r="K18" s="1">
+        <f>[1]PRETTO!$K$13</f>
+        <v>7.1708333333333334</v>
+      </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -4656,7 +4807,10 @@
         <f>[1]RENARD!$K$12</f>
         <v>0.5073085175058859</v>
       </c>
-      <c r="K19" s="1"/>
+      <c r="K19" s="1">
+        <f>[1]RENARD!$K$13</f>
+        <v>0.65105851750588584</v>
+      </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -4701,7 +4855,10 @@
         <f>[1]STOURME!$K$12</f>
         <v>1.6855555555555548</v>
       </c>
-      <c r="K20" s="1"/>
+      <c r="K20" s="1">
+        <f>[1]STOURME!$K$13</f>
+        <v>1.6737499999999992</v>
+      </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -4746,7 +4903,10 @@
         <f>[1]VALDES!$K$12</f>
         <v>1.4908333333333332</v>
       </c>
-      <c r="K21" s="1"/>
+      <c r="K21" s="1">
+        <f>[1]VALDES!$K$13</f>
+        <v>0.77069444444444435</v>
+      </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
@@ -4764,6 +4924,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1af87cbf-0b42-4b26-9f6b-99e2f2c26033">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100937BC018F9DBE74C924557264AE521C8" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df6304fc725e62364016da26349e6aa2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1af87cbf-0b42-4b26-9f6b-99e2f2c26033" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="24110c7d026aeb2113c3cc5af0e0c47a" ns2:_="">
     <xsd:import namespace="1af87cbf-0b42-4b26-9f6b-99e2f2c26033"/>
@@ -4947,26 +5126,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43162B4C-8036-4FD3-B02E-9FAB6E06A7E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1af87cbf-0b42-4b26-9f6b-99e2f2c26033"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1af87cbf-0b42-4b26-9f6b-99e2f2c26033">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5359EC-D85E-4EE8-994B-A84A38643895}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69449F73-ECCA-4049-9F77-5F6BD292D3D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4982,22 +5160,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5359EC-D85E-4EE8-994B-A84A38643895}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43162B4C-8036-4FD3-B02E-9FAB6E06A7E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1af87cbf-0b42-4b26-9f6b-99e2f2c26033"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>